--- a/HopDongVaBaoHiem.xlsx
+++ b/HopDongVaBaoHiem.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{934B06F5-A0D4-4F77-ABAB-C72B05479E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9599C309-B33F-47A5-8B97-CF0DD94F83EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D15556D2-2B15-4E64-94D9-3621949CCF05}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="55">
   <si>
     <t>Đặc tả use case</t>
   </si>
@@ -137,9 +137,6 @@
     </r>
   </si>
   <si>
-    <t>Quản lý hợp đồng</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -197,9 +194,6 @@
     <t>Trong cơ sở dữ liệu tồn tại ít nhất 1 hợp đồng</t>
   </si>
   <si>
-    <t>Quản lý lương</t>
-  </si>
-  <si>
     <t>Người dùng bấm vào Quản lý lương</t>
   </si>
   <si>
@@ -241,9 +235,6 @@
   </si>
   <si>
     <t>Lỗi cơ sở dữ liệu</t>
-  </si>
-  <si>
-    <t>Quản lý chấm công</t>
   </si>
   <si>
     <r>
@@ -300,7 +291,37 @@
     <t>Có thể thêm chấm công bằng QR</t>
   </si>
   <si>
-    <t>Mỗi ngày làm việc được xác định rõ</t>
+    <t>UC_03 Quản lý điểm danh</t>
+  </si>
+  <si>
+    <t>Đăng nhập hợp lệ</t>
+  </si>
+  <si>
+    <t>UC04 Quản lý lương</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Được tạo bởi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>P.Hải Đăng,Duy</t>
+    </r>
+  </si>
+  <si>
+    <t>UC 06 Quản lý hợp đồng</t>
   </si>
 </sst>
 </file>
@@ -530,6 +551,24 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -541,26 +580,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -916,23 +937,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="24"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="20"/>
       <c r="F1" s="4"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="17"/>
+      <c r="B2" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="23"/>
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -942,153 +963,153 @@
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="25">
         <v>46112</v>
       </c>
-      <c r="D3" s="17"/>
+      <c r="D3" s="23"/>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="17"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="23"/>
       <c r="F4" s="6"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="20"/>
+      <c r="B5" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="17"/>
       <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="20"/>
+      <c r="B6" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="F6" s="6"/>
     </row>
     <row r="7" spans="1:6" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="20"/>
+      <c r="B7" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17"/>
       <c r="F7" s="6"/>
     </row>
     <row r="8" spans="1:6" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="20"/>
+      <c r="B8" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17"/>
       <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="20"/>
+      <c r="B9" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17"/>
       <c r="F9" s="6"/>
     </row>
     <row r="10" spans="1:6" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="20"/>
+      <c r="B10" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="20"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="17"/>
       <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="20"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17"/>
       <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="20"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="17"/>
       <c r="F13" s="7"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="20"/>
+      <c r="B14" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="20"/>
+      <c r="B15" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="20"/>
+      <c r="B16" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
       <c r="F16" s="7"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1106,35 +1127,35 @@
       <c r="F18" s="7"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="24"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="20"/>
       <c r="F19" s="6"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="17"/>
+      <c r="B20" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="22"/>
+      <c r="D20" s="23"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="25">
         <v>46112</v>
       </c>
-      <c r="D21" s="17"/>
+      <c r="D21" s="23"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
@@ -1143,139 +1164,139 @@
       <c r="B22" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="23"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="20"/>
+      <c r="B23" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="D23" s="17"/>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="20"/>
+      <c r="B24" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17"/>
       <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="20"/>
+      <c r="B25" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17"/>
       <c r="F25" s="6"/>
     </row>
     <row r="26" spans="1:6" ht="97.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="20"/>
+      <c r="B26" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="F26" s="6"/>
     </row>
     <row r="27" spans="1:6" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="20"/>
+      <c r="B27" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="D27" s="17"/>
       <c r="F27" s="6"/>
     </row>
     <row r="28" spans="1:6" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="20"/>
+      <c r="B28" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="D28" s="17"/>
       <c r="F28" s="6"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="20"/>
+      <c r="B29" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="16"/>
+      <c r="D29" s="17"/>
       <c r="F29" s="6"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="20"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="F30" s="7"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="19"/>
-      <c r="D31" s="20"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="17"/>
       <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B32" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="20"/>
+      <c r="B32" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="16"/>
+      <c r="D32" s="17"/>
       <c r="F32" s="7"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B33" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" s="19"/>
-      <c r="D33" s="20"/>
+      <c r="B33" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="16"/>
+      <c r="D33" s="17"/>
       <c r="F33" s="6"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B34" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="20"/>
+      <c r="B34" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="F34" s="7"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1305,11 +1326,11 @@
       <c r="A38" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B38" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="B38" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="22"/>
+      <c r="D38" s="23"/>
       <c r="F38" s="7"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1319,143 +1340,143 @@
       <c r="B39" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="21">
+      <c r="C39" s="25">
         <v>46112</v>
       </c>
-      <c r="D39" s="17"/>
+      <c r="D39" s="23"/>
       <c r="F39" s="6"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="17"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="23"/>
       <c r="F40" s="7"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B41" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="20"/>
+      <c r="B41" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="16"/>
+      <c r="D41" s="17"/>
       <c r="F41" s="6"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42" s="19"/>
-      <c r="D42" s="20"/>
+      <c r="B42" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
     </row>
     <row r="43" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B43" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C43" s="19"/>
-      <c r="D43" s="20"/>
+      <c r="B43" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="16"/>
+      <c r="D43" s="17"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B44" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="C44" s="19"/>
-      <c r="D44" s="20"/>
+      <c r="B44" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" s="16"/>
+      <c r="D44" s="17"/>
     </row>
     <row r="45" spans="1:6" ht="135" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B45" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="C45" s="19"/>
-      <c r="D45" s="20"/>
+      <c r="B45" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="16"/>
+      <c r="D45" s="17"/>
     </row>
     <row r="46" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B46" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="C46" s="19"/>
-      <c r="D46" s="20"/>
+      <c r="B46" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C47" s="19"/>
-      <c r="D47" s="20"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="17"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B48" s="18" t="s">
+      <c r="B48" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="C48" s="19"/>
-      <c r="D48" s="20"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="17"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B49" s="18" t="s">
+      <c r="B49" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="C49" s="19"/>
-      <c r="D49" s="20"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="17"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B50" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="C50" s="19"/>
-      <c r="D50" s="20"/>
+      <c r="B50" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B51" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="C51" s="19"/>
-      <c r="D51" s="20"/>
+      <c r="B51" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C51" s="16"/>
+      <c r="D51" s="17"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B52" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C52" s="19"/>
-      <c r="D52" s="20"/>
+      <c r="B52" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C52" s="16"/>
+      <c r="D52" s="17"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F53" s="6"/>
@@ -1480,11 +1501,6 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="B51:D51"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
     <mergeCell ref="C40:D40"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B28:D28"/>
@@ -1516,6 +1532,11 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B16:D16"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
